--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npclist.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npclist.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="cfg_npclist" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_npclist!$A$1:$Q$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_npclist!$A$1:$Q$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="247">
   <si>
     <t>npcid</t>
   </si>
@@ -900,16 +901,366 @@
     <t>12</t>
   </si>
   <si>
+    <t>勇士！我能为你提供些帮助</t>
+  </si>
+  <si>
+    <t>dev/outui/NPC/Panel/KLNPCPhantomMentor/KLNPCPhantomMentorPanel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>流浪商人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海罗德</t>
+    </r>
+  </si>
+  <si>
+    <t>流浪商人</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>少女·安娜</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>100107</t>
+  </si>
+  <si>
+    <t>仓库使者·塞弗特</t>
+  </si>
+  <si>
+    <t>仓库</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>dev/ui/Bag/Panel/KLDepots/KLDepotsPanel#table:x=-415;y=0|dev/ui/Bag/Panel/KLUIBag/KLUIBagPanel</t>
+  </si>
+  <si>
+    <t>100108</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>100109</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>100110</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>100111</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>100112</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>警卫队长摩伦（220级二转）</t>
+  </si>
+  <si>
+    <t>二转</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666605;2=666607</t>
+  </si>
+  <si>
+    <t>精灵·安吉拉</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#5</t>
+  </si>
+  <si>
+    <t>20021</t>
+  </si>
+  <si>
+    <t>100402</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>100403</t>
+  </si>
+  <si>
+    <t>工匠·尤达</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#4</t>
+  </si>
+  <si>
+    <t>100404</t>
+  </si>
+  <si>
+    <t>合成·玛雅哥布林</t>
+  </si>
+  <si>
+    <t>合成</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=1;2=2;3=3;4=4;5=5;6=6;7=7;8=8;9=9</t>
+  </si>
+  <si>
+    <t>20020</t>
+  </si>
+  <si>
+    <t>100405</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>100406</t>
+  </si>
+  <si>
+    <t>恶魔广场守卫·卡隆</t>
+  </si>
+  <si>
+    <t>恶魔广场</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#10001</t>
+  </si>
+  <si>
+    <t>100407</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>100408</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>105201</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>105202</t>
+  </si>
+  <si>
+    <t>流浪商人·塞尔维亚</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>105203</t>
+  </si>
+  <si>
+    <t>召唤师·摩尔塞</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>105204</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>105205</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>105206</t>
+  </si>
+  <si>
+    <t>100301</t>
+  </si>
+  <si>
+    <t>战盟使者·罗斯</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>战盟</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>你好，勇士！我能为你提供些帮助</t>
   </si>
   <si>
+    <t>100302</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>100303</t>
+  </si>
+  <si>
+    <t>武器商人·苏菲</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>100304</t>
+  </si>
+  <si>
+    <t>魔导师·露茜</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>100305</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>流浪商人</t>
+      <t>老板娘</t>
     </r>
     <r>
       <rPr>
@@ -925,89 +1276,186 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>海罗德</t>
-    </r>
-  </si>
-  <si>
-    <t>流浪商人</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>少女·安娜</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>100107</t>
-  </si>
-  <si>
-    <t>仓库使者·塞弗特</t>
-  </si>
-  <si>
-    <t>仓库</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>dev/ui/Bag/Panel/KLDepots/KLDepotsPanel#table:x=-415;y=0|dev/ui/Bag/Panel/KLUIBag/KLUIBagPanel</t>
-  </si>
-  <si>
-    <t>100108</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>dev/outui/NPC/Panel/KLNPCPhantomMentor/KLNPCPhantomMentorPanel</t>
-  </si>
-  <si>
-    <t>100109</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>100110</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>100111</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>100112</t>
-  </si>
-  <si>
-    <t>109</t>
+      <t>莉娜</t>
+    </r>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>100306</t>
+  </si>
+  <si>
+    <t>血色城堡守卫·大天使的使者</t>
+  </si>
+  <si>
+    <t>血色城堡</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#11001</t>
+  </si>
+  <si>
+    <t>0#-6#0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圣导士塞维娜（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>级一转）</t>
+    </r>
+  </si>
+  <si>
+    <t>一转</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666601;2=666603</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>100308</t>
+  </si>
+  <si>
+    <t>警卫队长</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>101201</t>
+  </si>
+  <si>
+    <t>受伤的大天使</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLBloodTip/KLBloodTipPanel#101201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>艾德</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>萤之石管理员</t>
+    </r>
+  </si>
+  <si>
+    <t>萤石管理</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLGemSynthesis/KLGemSynthesisPanel</t>
+  </si>
+  <si>
+    <t>弟子黛彬（380级三转）</t>
+  </si>
+  <si>
+    <t>三转</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666609</t>
+  </si>
+  <si>
+    <t>摩斯</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=8</t>
+  </si>
+  <si>
+    <t>暗黑血狼人扩雷</t>
+  </si>
+  <si>
+    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70001</t>
+  </si>
+  <si>
+    <t>守卫</t>
+  </si>
+  <si>
+    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70002</t>
+  </si>
+  <si>
+    <t>驯兽师</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=10;2=11;3=12</t>
+  </si>
+  <si>
+    <t>100309</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>100310</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666609;2=666611;3=666613;4=6666091</t>
   </si>
   <si>
     <t>赤色要塞报名官</t>
@@ -1020,445 +1468,6 @@
   </si>
   <si>
     <t>dev/outui/Activity/Panel/KLRedFort/KLRedFortPanel</t>
-  </si>
-  <si>
-    <t>警卫队长摩伦</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666605;2=666607</t>
-  </si>
-  <si>
-    <t>精灵·安吉拉</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#5</t>
-  </si>
-  <si>
-    <t>20021</t>
-  </si>
-  <si>
-    <t>100402</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>100403</t>
-  </si>
-  <si>
-    <t>工匠·尤达</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#4</t>
-  </si>
-  <si>
-    <t>100404</t>
-  </si>
-  <si>
-    <t>合成·玛雅哥布林</t>
-  </si>
-  <si>
-    <t>合成</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=1;2=2;3=3;4=4;5=5;6=6;7=7;8=8;9=9</t>
-  </si>
-  <si>
-    <t>20020</t>
-  </si>
-  <si>
-    <t>100405</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>100406</t>
-  </si>
-  <si>
-    <t>恶魔广场守卫·卡隆</t>
-  </si>
-  <si>
-    <t>恶魔广场</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#10001</t>
-  </si>
-  <si>
-    <t>100407</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>100408</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>105201</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>105202</t>
-  </si>
-  <si>
-    <t>流浪商人·塞尔维亚</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>105203</t>
-  </si>
-  <si>
-    <t>召唤师·摩尔塞</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>105204</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>105205</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>105206</t>
-  </si>
-  <si>
-    <t>100301</t>
-  </si>
-  <si>
-    <t>战盟使者·罗斯</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>战盟</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>100302</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>100303</t>
-  </si>
-  <si>
-    <t>武器商人·苏菲</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>100304</t>
-  </si>
-  <si>
-    <t>魔导师·露茜</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#33</t>
-  </si>
-  <si>
-    <t>100305</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>老板娘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>莉娜</t>
-    </r>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>100306</t>
-  </si>
-  <si>
-    <t>血色城堡守卫·大天使的使者</t>
-  </si>
-  <si>
-    <t>血色城堡</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#11001</t>
-  </si>
-  <si>
-    <t>0#-6#0</t>
-  </si>
-  <si>
-    <t>圣导士塞维娜</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666601;2=666603</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>100308</t>
-  </si>
-  <si>
-    <t>警卫队长</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>100309</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>100310</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>100201</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>100501</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>100801</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>101201</t>
-  </si>
-  <si>
-    <t>受伤的大天使</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLBloodTip/KLBloodTipPanel#101201</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>艾德</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>萤之石管理员</t>
-    </r>
-  </si>
-  <si>
-    <t>萤石管理</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLGemSynthesis/KLGemSynthesisPanel</t>
-  </si>
-  <si>
-    <t>弟子黛彬</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666609;2=666611;3=666613;4=6666091</t>
-  </si>
-  <si>
-    <t>摩斯</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=8</t>
-  </si>
-  <si>
-    <t>暗黑血狼人扩雷</t>
-  </si>
-  <si>
-    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70001</t>
-  </si>
-  <si>
-    <t>守卫</t>
-  </si>
-  <si>
-    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70002</t>
-  </si>
-  <si>
-    <t>驯兽师</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=10;2=11;3=12</t>
   </si>
 </sst>
 </file>
@@ -2093,6 +2102,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2101,9 +2113,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2650,7 +2659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2725,7 +2734,7 @@
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -2743,7 +2752,7 @@
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -2752,7 +2761,7 @@
       <c r="K2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -2890,7 +2899,7 @@
       <c r="D5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2934,7 +2943,7 @@
       <c r="A6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -3049,10 +3058,12 @@
       <c r="I8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L8"/>
+      <c r="L8" t="s">
+        <v>89</v>
+      </c>
       <c r="M8" s="1" t="s">
         <v>66</v>
       </c>
@@ -3073,26 +3084,26 @@
       <c r="A9" s="1">
         <v>100105</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>89</v>
+      <c r="B9" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>63</v>
@@ -3121,19 +3132,19 @@
         <v>100106</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>63</v>
@@ -3160,25 +3171,25 @@
     </row>
     <row r="11" ht="16.5" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>100</v>
+      <c r="D11" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>68</v>
@@ -3191,7 +3202,7 @@
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>66</v>
@@ -3211,7 +3222,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>83</v>
@@ -3223,10 +3234,10 @@
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>87</v>
@@ -3234,12 +3245,12 @@
       <c r="I12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>66</v>
@@ -3282,11 +3293,11 @@
       <c r="I13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>88</v>
       </c>
       <c r="L13" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>66</v>
@@ -3329,11 +3340,11 @@
       <c r="I14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="L14" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>66</v>
@@ -3371,7 +3382,7 @@
         <v>114</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>87</v>
@@ -3379,11 +3390,11 @@
       <c r="I15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="L15" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>66</v>
@@ -3406,19 +3417,19 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>100</v>
+      <c r="D16" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>116</v>
@@ -3433,7 +3444,7 @@
         <v>64</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>66</v>
@@ -3453,39 +3464,36 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1">
-        <v>100113</v>
-      </c>
-      <c r="B17" s="5" t="s">
+        <v>100114</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="1">
-        <v>130</v>
+      <c r="F17" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="G17" s="1">
-        <v>134</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>30</v>
+      </c>
+      <c r="H17" s="1">
+        <v>57</v>
       </c>
       <c r="I17" s="1">
         <v>3</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" t="s">
         <v>120</v>
       </c>
       <c r="M17" s="1" t="s">
@@ -3493,9 +3501,6 @@
       </c>
       <c r="N17" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>68</v>
@@ -3506,35 +3511,34 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1">
-        <v>100114</v>
-      </c>
-      <c r="B18" s="5" t="s">
+        <v>100401</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="1">
-        <v>107</v>
-      </c>
-      <c r="G18" s="1">
-        <v>86</v>
-      </c>
-      <c r="H18" s="1">
-        <v>57</v>
+        <v>122</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L18" t="s">
-        <v>122</v>
+        <v>64</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>66</v>
@@ -3542,6 +3546,9 @@
       <c r="N18" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="O18" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="P18" s="1" t="s">
         <v>68</v>
       </c>
@@ -3550,35 +3557,38 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="1">
-        <v>100401</v>
+      <c r="A19" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>64</v>
+      <c r="J19" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>128</v>
+      <c r="L19" t="s">
+        <v>89</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>66</v>
@@ -3587,7 +3597,7 @@
         <v>67</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>68</v>
@@ -3601,34 +3611,31 @@
         <v>130</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L20" t="s">
-        <v>107</v>
+      <c r="L20" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>66</v>
@@ -3648,22 +3655,28 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>63</v>
@@ -3671,11 +3684,11 @@
       <c r="J21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>137</v>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>66</v>
@@ -3684,7 +3697,7 @@
         <v>67</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>68</v>
@@ -3695,40 +3708,40 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>140</v>
+        <v>122</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>144</v>
+      <c r="K22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>66</v>
@@ -3737,7 +3750,7 @@
         <v>67</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>68</v>
@@ -3751,25 +3764,25 @@
         <v>146</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>100</v>
+        <v>122</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>69</v>
@@ -3781,7 +3794,7 @@
         <v>64</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>66</v>
@@ -3801,40 +3814,37 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>122</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>154</v>
+      <c r="L24" t="s">
+        <v>89</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>66</v>
@@ -3854,22 +3864,22 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>87</v>
@@ -3877,14 +3887,14 @@
       <c r="I25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>66</v>
@@ -3904,37 +3914,34 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L26" t="s">
-        <v>107</v>
+      <c r="L26" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>66</v>
@@ -3954,22 +3961,22 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>63</v>
@@ -3981,7 +3988,7 @@
         <v>64</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>66</v>
@@ -4001,30 +4008,33 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>64</v>
       </c>
       <c r="M28" s="1" t="s">
@@ -4045,34 +4055,37 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>64</v>
+      <c r="J29" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>64</v>
+      <c r="L29" t="s">
+        <v>89</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>66</v>
@@ -4092,19 +4105,19 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>175</v>
@@ -4113,16 +4126,16 @@
         <v>87</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>66</v>
@@ -4148,31 +4161,31 @@
         <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>87</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>66</v>
@@ -4192,37 +4205,40 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>84</v>
+        <v>179</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L32" t="s">
-        <v>107</v>
+      <c r="L32" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>66</v>
@@ -4242,40 +4258,40 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>182</v>
+      <c r="D33" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>66</v>
@@ -4295,31 +4311,25 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>64</v>
@@ -4327,9 +4337,7 @@
       <c r="K34" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="L34"/>
       <c r="M34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4348,22 +4356,22 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>69</v>
@@ -4374,7 +4382,9 @@
       <c r="K35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L35"/>
+      <c r="L35" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="M35" s="1" t="s">
         <v>66</v>
       </c>
@@ -4393,40 +4403,40 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>64</v>
+      <c r="J36" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L36" t="s">
-        <v>198</v>
+      <c r="L36" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>66</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>64</v>
@@ -4440,40 +4450,46 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L37" t="s">
-        <v>198</v>
+      <c r="L37" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>204</v>
+        <v>67</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>64</v>
@@ -4486,44 +4502,41 @@
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>206</v>
+      <c r="A38" s="1">
+        <v>100307</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>59</v>
+        <v>179</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>208</v>
+        <v>119</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>210</v>
+      <c r="L38" t="s">
+        <v>214</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>67</v>
@@ -4532,42 +4545,42 @@
         <v>64</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="1">
-        <v>100307</v>
+      <c r="A39" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L39" t="s">
-        <v>216</v>
+      <c r="L39" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>66</v>
@@ -4579,42 +4592,48 @@
         <v>64</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>181</v>
+        <v>221</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>174</v>
+        <v>62</v>
+      </c>
+      <c r="H40" s="1">
+        <v>50</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>66</v>
@@ -4626,45 +4645,48 @@
         <v>64</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>87</v>
+      <c r="A41" s="1">
+        <v>100901</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1052</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46</v>
+      </c>
+      <c r="G41" s="1">
+        <v>243</v>
+      </c>
+      <c r="H41" s="1">
+        <v>24</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>64</v>
+        <v>64</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>66</v>
@@ -4672,9 +4694,6 @@
       <c r="N41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P41" s="1" t="s">
         <v>68</v>
       </c>
@@ -4683,38 +4702,35 @@
       </c>
     </row>
     <row r="42" spans="1:17">
-      <c r="A42" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>84</v>
+      <c r="A42" s="1">
+        <v>100902</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="1">
+        <v>28</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1">
+        <v>3</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="L42" t="s">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>66</v>
@@ -4722,9 +4738,6 @@
       <c r="N42" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P42" s="1" t="s">
         <v>68</v>
       </c>
@@ -4733,38 +4746,35 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="1">
+        <v>100903</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1052</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" s="1">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1">
         <v>225</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="H43" s="1">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="L43" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>66</v>
@@ -4772,9 +4782,6 @@
       <c r="N43" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P43" s="1" t="s">
         <v>68</v>
       </c>
@@ -4783,38 +4790,33 @@
       </c>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J44" s="1" t="s">
+      <c r="A44" s="1">
+        <v>100904</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1035</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="F44" s="1">
+        <v>62</v>
+      </c>
+      <c r="G44" s="1">
+        <v>239</v>
+      </c>
+      <c r="H44" s="1">
+        <v>49</v>
+      </c>
+      <c r="I44" s="1">
+        <v>4</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="L44" t="s">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>66</v>
@@ -4822,9 +4824,6 @@
       <c r="N44" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P44" s="1" t="s">
         <v>68</v>
       </c>
@@ -4833,38 +4832,33 @@
       </c>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="A45" s="1">
+        <v>100905</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1042</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="F45" s="1">
         <v>119</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="G45" s="1">
+        <v>168</v>
+      </c>
+      <c r="H45" s="1">
+        <v>14</v>
+      </c>
+      <c r="I45" s="4">
+        <v>3</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="L45" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>66</v>
@@ -4872,9 +4866,6 @@
       <c r="N45" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P45" s="1" t="s">
         <v>68</v>
       </c>
@@ -4883,41 +4874,36 @@
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>235</v>
+      <c r="A46" s="1">
+        <v>100120</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="1">
+        <v>122</v>
+      </c>
+      <c r="G46" s="1">
+        <v>114</v>
+      </c>
+      <c r="H46" s="1">
+        <v>28</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>237</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H46" s="1">
-        <v>50</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>66</v>
@@ -4925,9 +4911,6 @@
       <c r="N46" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O46" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="P46" s="1" t="s">
         <v>68</v>
       </c>
@@ -4936,271 +4919,17 @@
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="1">
-        <v>100901</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1052</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="1">
-        <v>46</v>
-      </c>
-      <c r="G47" s="1">
-        <v>243</v>
-      </c>
-      <c r="H47" s="1">
-        <v>24</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
       <c r="L47" t="s">
-        <v>241</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="1">
-        <v>100902</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1035</v>
-      </c>
-      <c r="F48" s="1">
-        <v>228</v>
-      </c>
-      <c r="G48" s="1">
-        <v>48</v>
-      </c>
-      <c r="H48" s="1">
-        <v>20</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L48" t="s">
-        <v>243</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" s="1">
-        <v>100903</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1052</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="1">
-        <v>22</v>
-      </c>
-      <c r="G49" s="1">
-        <v>225</v>
-      </c>
-      <c r="H49" s="1">
-        <v>28</v>
-      </c>
-      <c r="I49" s="1">
-        <v>2</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L49" t="s">
-        <v>245</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17">
-      <c r="A50" s="1">
-        <v>100904</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1035</v>
-      </c>
-      <c r="D50" s="5"/>
-      <c r="F50" s="1">
-        <v>62</v>
-      </c>
-      <c r="G50" s="1">
-        <v>239</v>
-      </c>
-      <c r="H50" s="1">
-        <v>49</v>
-      </c>
-      <c r="I50" s="1">
-        <v>4</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L50" t="s">
-        <v>247</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17">
-      <c r="A51" s="1">
-        <v>100905</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C51" s="1">
-        <v>1042</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="F51" s="1">
-        <v>119</v>
-      </c>
-      <c r="G51" s="1">
-        <v>168</v>
-      </c>
-      <c r="H51" s="1">
-        <v>14</v>
-      </c>
-      <c r="I51" s="3">
-        <v>3</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L51" t="s">
-        <v>249</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17">
-      <c r="A52" s="1">
-        <v>100120</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="1">
-        <v>122</v>
-      </c>
-      <c r="G52" s="1">
-        <v>114</v>
-      </c>
-      <c r="H52" s="1">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q52" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q48" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="K10 K11 K12">
@@ -5209,4 +4938,174 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A4:Q20"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="4" s="1" customFormat="1" spans="1:17">
+      <c r="A4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:17">
+      <c r="A5" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:17">
+      <c r="A20" s="1">
+        <v>100113</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="1">
+        <v>130</v>
+      </c>
+      <c r="G20" s="1">
+        <v>134</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npclist.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npclist.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_npclist" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="261">
   <si>
     <t>npcid</t>
   </si>
@@ -135,7 +135,22 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>NPC小地图显示图标，填写文件名称；不填则不显示图标</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小地图显示图标，填写文件名称；不填则不显示图标</t>
+    </r>
   </si>
   <si>
     <t>NPC所在X轴坐标</t>
@@ -752,13 +767,13 @@
     <t>100101</t>
   </si>
   <si>
-    <t>酒吧老板娘·莉亚</t>
+    <t>Bar Landlady・Leah</t>
   </si>
   <si>
     <t>1001</t>
   </si>
   <si>
-    <t>酒吧老板娘</t>
+    <t>Leah</t>
   </si>
   <si>
     <t>img_minimap__npc</t>
@@ -800,27 +815,30 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>铁匠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>汉斯</t>
-    </r>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Blacksmith</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hans</t>
+    </r>
+  </si>
+  <si>
+    <t>Hans</t>
   </si>
   <si>
     <t>116</t>
@@ -853,7 +871,33 @@
     <t>100103</t>
   </si>
   <si>
-    <t>魔导师·帕希</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Magician</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Pasi</t>
+    </r>
+  </si>
+  <si>
+    <t>Pasi</t>
   </si>
   <si>
     <t>118</t>
@@ -871,6 +915,754 @@
     <t>100104</t>
   </si>
   <si>
+    <t>Phantom Mentor・Katie</t>
+  </si>
+  <si>
+    <t>Katie</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Warrior! May I offer you assistance?</t>
+  </si>
+  <si>
+    <t>dev/outui/NPC/Panel/KLNPCPhantomMentor/KLNPCPhantomMentorPanel</t>
+  </si>
+  <si>
+    <t>Wandering Merchant・Herod</t>
+  </si>
+  <si>
+    <t>Herod</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Young Girl・Anna</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>100107</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Storage Keeper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Seifert</t>
+    </r>
+  </si>
+  <si>
+    <t>Seifert</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>dev/ui/Bag/Panel/KLDepots/KLDepotsPanel#table:x=-415;y=0|dev/ui/Bag/Panel/KLUIBag/KLUIBagPanel</t>
+  </si>
+  <si>
+    <t>100108</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>100109</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>100110</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>100111</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>100112</t>
+  </si>
+  <si>
+    <t>Storage Keeper・Seifert</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Captain Moren (220Lv 2nd Quest)</t>
+  </si>
+  <si>
+    <t>Moren</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666605;2=666607</t>
+  </si>
+  <si>
+    <t>Elf・Angela</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#5</t>
+  </si>
+  <si>
+    <t>20021</t>
+  </si>
+  <si>
+    <t>100402</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>100403</t>
+  </si>
+  <si>
+    <t>Craftsman・Yuda</t>
+  </si>
+  <si>
+    <t>Yuda</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#4</t>
+  </si>
+  <si>
+    <t>100404</t>
+  </si>
+  <si>
+    <t>Chaos Goblin</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=1;2=2;3=3;4=4;5=5;6=6;7=7;8=8</t>
+  </si>
+  <si>
+    <t>20020</t>
+  </si>
+  <si>
+    <t>100405</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>100406</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Devil Square Guard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Karon</t>
+    </r>
+  </si>
+  <si>
+    <t>Karon</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#10001</t>
+  </si>
+  <si>
+    <t>100407</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Phantom Mentor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Katie</t>
+    </r>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>100408</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>105201</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>105202</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Wandering Merchant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Serbia</t>
+    </r>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>105203</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Summoner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Morsay</t>
+    </r>
+  </si>
+  <si>
+    <t>Morsay</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>105204</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>105205</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>105206</t>
+  </si>
+  <si>
+    <t>100301</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Guild Messenger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Ross</t>
+    </r>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>Ross</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>100302</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>100303</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Weapon Merchant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Sophie</t>
+    </r>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>100304</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Magician</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lucy</t>
+    </r>
+  </si>
+  <si>
+    <t>Lucy</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>100305</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Landlady</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lina</t>
+    </r>
+  </si>
+  <si>
+    <t>Lina</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>100306</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Blood Castle Guard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Archangel Messenger</t>
+    </r>
+  </si>
+  <si>
+    <t>Archangel Messenger</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#11001</t>
+  </si>
+  <si>
+    <t>0#-6#0</t>
+  </si>
+  <si>
+    <t>Muse Serverina (150Lv 1st Quest)</t>
+  </si>
+  <si>
+    <t>Serverina</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666601;2=666603</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>100308</t>
+  </si>
+  <si>
+    <t>Captain Guard</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>101201</t>
+  </si>
+  <si>
+    <t>Wounded Archangel</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>dev/outui/Activity/Panel/KLBloodTip/KLBloodTipPanel#101201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Ed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Fluorite Manager</t>
+    </r>
+  </si>
+  <si>
+    <t>Ed</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLGemSynthesis/KLGemSynthesisPanel</t>
+  </si>
+  <si>
+    <t>Disciple Davin (380Lv 3rd Quest)</t>
+  </si>
+  <si>
+    <t>Davin</t>
+  </si>
+  <si>
+    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666609</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=8</t>
+  </si>
+  <si>
+    <t>Dark Werewolf Kure</t>
+  </si>
+  <si>
+    <t>Kure</t>
+  </si>
+  <si>
+    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70001</t>
+  </si>
+  <si>
+    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70002</t>
+  </si>
+  <si>
+    <t>Tamer</t>
+  </si>
+  <si>
+    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=9;2=10;3=11;4=12;5=13</t>
+  </si>
+  <si>
+    <t>100309</t>
+  </si>
+  <si>
     <t>幻影导师·凯蒂</t>
   </si>
   <si>
@@ -892,561 +1684,10 @@
     </r>
   </si>
   <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>勇士！我能为你提供些帮助</t>
-  </si>
-  <si>
-    <t>dev/outui/NPC/Panel/KLNPCPhantomMentor/KLNPCPhantomMentorPanel</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>流浪商人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>海罗德</t>
-    </r>
-  </si>
-  <si>
-    <t>流浪商人</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>少女·安娜</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>100107</t>
-  </si>
-  <si>
-    <t>仓库使者·塞弗特</t>
-  </si>
-  <si>
-    <t>仓库</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>dev/ui/Bag/Panel/KLDepots/KLDepotsPanel#table:x=-415;y=0|dev/ui/Bag/Panel/KLUIBag/KLUIBagPanel</t>
-  </si>
-  <si>
-    <t>100108</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>100109</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>100110</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>100111</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>100112</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>警卫队长摩伦（220级二转）</t>
-  </si>
-  <si>
-    <t>二转</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666605;2=666607</t>
-  </si>
-  <si>
-    <t>精灵·安吉拉</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#5</t>
-  </si>
-  <si>
-    <t>20021</t>
-  </si>
-  <si>
-    <t>100402</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>100403</t>
-  </si>
-  <si>
-    <t>工匠·尤达</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>dev/ui/NPC/Panel/KLNPCShop/KLNPCShopPanel#4</t>
-  </si>
-  <si>
-    <t>100404</t>
-  </si>
-  <si>
-    <t>合成·玛雅哥布林</t>
-  </si>
-  <si>
-    <t>合成</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=1;2=2;3=3;4=4;5=5;6=6;7=7;8=8;9=9</t>
-  </si>
-  <si>
-    <t>20020</t>
-  </si>
-  <si>
-    <t>100405</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>100406</t>
-  </si>
-  <si>
-    <t>恶魔广场守卫·卡隆</t>
-  </si>
-  <si>
-    <t>恶魔广场</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#10001</t>
-  </si>
-  <si>
-    <t>100407</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>100408</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>105201</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>105202</t>
-  </si>
-  <si>
-    <t>流浪商人·塞尔维亚</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>105203</t>
-  </si>
-  <si>
-    <t>召唤师·摩尔塞</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>105204</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>105205</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>105206</t>
-  </si>
-  <si>
-    <t>100301</t>
-  </si>
-  <si>
-    <t>战盟使者·罗斯</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>战盟</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>178</t>
   </si>
   <si>
     <t>你好，勇士！我能为你提供些帮助</t>
-  </si>
-  <si>
-    <t>100302</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>100303</t>
-  </si>
-  <si>
-    <t>武器商人·苏菲</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>100304</t>
-  </si>
-  <si>
-    <t>魔导师·露茜</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>100305</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>老板娘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>莉娜</t>
-    </r>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>100306</t>
-  </si>
-  <si>
-    <t>血色城堡守卫·大天使的使者</t>
-  </si>
-  <si>
-    <t>血色城堡</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#11001</t>
-  </si>
-  <si>
-    <t>0#-6#0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>圣导士塞维娜（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>150</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>级一转）</t>
-    </r>
-  </si>
-  <si>
-    <t>一转</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666601;2=666603</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>100308</t>
-  </si>
-  <si>
-    <t>警卫队长</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>101201</t>
-  </si>
-  <si>
-    <t>受伤的大天使</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>dev/outui/Activity/Panel/KLBloodTip/KLBloodTipPanel#101201</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>艾德</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>萤之石管理员</t>
-    </r>
-  </si>
-  <si>
-    <t>萤石管理</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLGemSynthesis/KLGemSynthesisPanel</t>
-  </si>
-  <si>
-    <t>弟子黛彬（380级三转）</t>
-  </si>
-  <si>
-    <t>三转</t>
-  </si>
-  <si>
-    <t>dev/outui/Task/Panel/KLTaskAccept/KLTaskAcceptPanel#table:1=666609</t>
-  </si>
-  <si>
-    <t>摩斯</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=8</t>
-  </si>
-  <si>
-    <t>暗黑血狼人扩雷</t>
-  </si>
-  <si>
-    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70001</t>
-  </si>
-  <si>
-    <t>守卫</t>
-  </si>
-  <si>
-    <t>dev/outui/Tips/Panel/KLClickNPCTransferTips/KLClickNPCTransferTipsPanel#70002</t>
-  </si>
-  <si>
-    <t>驯兽师</t>
-  </si>
-  <si>
-    <t>dev/outui/Synthesis/Panel/KLSynthesisMenu/KLSynthesisMenuPanel#table:1=10;2=11;3=12</t>
-  </si>
-  <si>
-    <t>100309</t>
-  </si>
-  <si>
-    <t>178</t>
   </si>
   <si>
     <t>100310</t>
@@ -1480,7 +1721,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1647,6 +1888,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS Gothic"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2114,8 +2360,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2740,7 +2986,7 @@
       <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2890,13 +3136,13 @@
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -2943,17 +3189,20 @@
       <c r="A6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>69</v>
@@ -2968,7 +3217,7 @@
         <v>64</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>66</v>
@@ -2977,7 +3226,7 @@
         <v>67</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>68</v>
@@ -2988,22 +3237,25 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="1" t="s">
         <v>77</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>69</v>
@@ -3015,7 +3267,7 @@
         <v>64</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>66</v>
@@ -3035,34 +3287,34 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>84</v>
+      <c r="D8" t="s">
+        <v>86</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>66</v>
@@ -3084,26 +3336,26 @@
       <c r="A9" s="1">
         <v>100105</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>90</v>
+      <c r="B9" t="s">
+        <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>91</v>
+      <c r="D9" t="s">
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>63</v>
@@ -3131,20 +3383,23 @@
       <c r="A10" s="1">
         <v>100106</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>95</v>
+      <c r="B10" t="s">
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>63</v>
@@ -3152,7 +3407,7 @@
       <c r="J10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="6"/>
+      <c r="K10" s="7"/>
       <c r="M10" s="1" t="s">
         <v>66</v>
       </c>
@@ -3171,25 +3426,25 @@
     </row>
     <row r="11" ht="16.5" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>68</v>
@@ -3200,9 +3455,9 @@
       <c r="J11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="6"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>66</v>
@@ -3222,35 +3477,35 @@
     </row>
     <row r="12" ht="16.5" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>84</v>
+      <c r="D12" t="s">
+        <v>86</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K12" s="6"/>
+      <c r="J12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="7"/>
       <c r="L12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>66</v>
@@ -3270,34 +3525,34 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>84</v>
+      <c r="D13" t="s">
+        <v>86</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>88</v>
+      <c r="J13" t="s">
+        <v>90</v>
       </c>
       <c r="L13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>66</v>
@@ -3317,34 +3572,34 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>84</v>
+      <c r="D14" t="s">
+        <v>86</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>88</v>
+      <c r="J14" t="s">
+        <v>90</v>
       </c>
       <c r="L14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>66</v>
@@ -3364,37 +3619,37 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>83</v>
+        <v>116</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>84</v>
+      <c r="D15" t="s">
+        <v>86</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>88</v>
+      <c r="J15" t="s">
+        <v>90</v>
       </c>
       <c r="L15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>66</v>
@@ -3414,25 +3669,25 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>100</v>
+        <v>118</v>
+      </c>
+      <c r="B16" t="s">
+        <v>119</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>101</v>
+      <c r="D16" t="s">
+        <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>68</v>
@@ -3444,7 +3699,7 @@
         <v>64</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>66</v>
@@ -3466,20 +3721,20 @@
       <c r="A17" s="1">
         <v>100114</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>117</v>
+      <c r="B17" t="s">
+        <v>121</v>
       </c>
       <c r="C17" s="1">
         <v>1003</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>118</v>
+      <c r="D17" t="s">
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G17" s="1">
         <v>30</v>
@@ -3490,11 +3745,11 @@
       <c r="I17" s="1">
         <v>3</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>88</v>
+      <c r="J17" t="s">
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>66</v>
@@ -3513,20 +3768,23 @@
       <c r="A18" s="1">
         <v>100401</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>121</v>
+      <c r="B18" t="s">
+        <v>125</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
+        <v>127</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>63</v>
@@ -3538,7 +3796,7 @@
         <v>64</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>66</v>
@@ -3547,7 +3805,7 @@
         <v>67</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>68</v>
@@ -3558,37 +3816,37 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>84</v>
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>88</v>
+      <c r="J19" t="s">
+        <v>90</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>66</v>
@@ -3608,22 +3866,25 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>63</v>
@@ -3635,7 +3896,7 @@
         <v>64</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>66</v>
@@ -3655,28 +3916,28 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
+      </c>
+      <c r="B21" t="s">
+        <v>143</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>143</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>63</v>
@@ -3687,8 +3948,8 @@
       <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>142</v>
+      <c r="L21" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>66</v>
@@ -3697,7 +3958,7 @@
         <v>67</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>68</v>
@@ -3708,25 +3969,25 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>100</v>
+        <v>149</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>68</v>
@@ -3741,7 +4002,7 @@
         <v>64</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>66</v>
@@ -3761,28 +4022,28 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>69</v>
@@ -3794,7 +4055,7 @@
         <v>64</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>66</v>
@@ -3814,37 +4075,37 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>83</v>
+        <v>158</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J24" t="s">
+        <v>90</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>66</v>
@@ -3864,37 +4125,37 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>162</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J25" t="s">
+        <v>90</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>66</v>
@@ -3914,19 +4175,22 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>100</v>
+        <v>165</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>68</v>
@@ -3941,7 +4205,7 @@
         <v>64</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>66</v>
@@ -3961,22 +4225,25 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>63</v>
@@ -4008,25 +4275,28 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>160</v>
+      <c r="D28" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>64</v>
@@ -4055,37 +4325,37 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>83</v>
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J29" t="s">
+        <v>90</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>66</v>
@@ -4105,37 +4375,37 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>182</v>
+      </c>
+      <c r="B30" t="s">
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>88</v>
+      <c r="J30" t="s">
+        <v>90</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>66</v>
@@ -4155,37 +4425,37 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>88</v>
+      <c r="J31" t="s">
+        <v>90</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>66</v>
@@ -4205,34 +4475,34 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>184</v>
+      <c r="J32" t="s">
+        <v>90</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>64</v>
@@ -4258,25 +4528,25 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>100</v>
+        <v>192</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>68</v>
@@ -4291,7 +4561,7 @@
         <v>64</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>66</v>
@@ -4311,22 +4581,25 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>69</v>
@@ -4356,22 +4629,25 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>69</v>
@@ -4403,28 +4679,31 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>88</v>
+      <c r="J36" t="s">
+        <v>90</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>64</v>
@@ -4436,7 +4715,7 @@
         <v>66</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>64</v>
@@ -4450,28 +4729,28 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>63</v>
@@ -4483,10 +4762,10 @@
         <v>64</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>67</v>
@@ -4505,35 +4784,35 @@
       <c r="A38" s="1">
         <v>100307</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>210</v>
+      <c r="B38" t="s">
+        <v>220</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J38" t="s">
+        <v>90</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>66</v>
@@ -4545,36 +4824,39 @@
         <v>64</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
+      </c>
+      <c r="B39" t="s">
+        <v>227</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J39" t="s">
+        <v>90</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>64</v>
@@ -4592,30 +4874,30 @@
         <v>64</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
+      </c>
+      <c r="B40" t="s">
+        <v>231</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>62</v>
@@ -4626,14 +4908,14 @@
       <c r="I40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>88</v>
+      <c r="J40" t="s">
+        <v>90</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>66</v>
@@ -4655,14 +4937,14 @@
       <c r="A41" s="1">
         <v>100901</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>224</v>
+      <c r="B41" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="C41" s="1">
         <v>1052</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>225</v>
+      <c r="D41" t="s">
+        <v>236</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>59</v>
@@ -4686,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>66</v>
@@ -4705,17 +4987,17 @@
       <c r="A42" s="1">
         <v>100902</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>227</v>
+      <c r="B42" t="s">
+        <v>238</v>
       </c>
       <c r="C42" s="1">
         <v>1003</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>228</v>
+      <c r="D42" t="s">
+        <v>239</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G42" s="1">
         <v>28</v>
@@ -4726,11 +5008,11 @@
       <c r="I42" s="1">
         <v>3</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>88</v>
+      <c r="J42" t="s">
+        <v>90</v>
       </c>
       <c r="L42" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>66</v>
@@ -4749,14 +5031,14 @@
       <c r="A43" s="1">
         <v>100903</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>230</v>
+      <c r="B43" t="s">
+        <v>241</v>
       </c>
       <c r="C43" s="1">
         <v>1052</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="F43" s="1">
         <v>22</v>
@@ -4770,11 +5052,11 @@
       <c r="I43" s="1">
         <v>2</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>88</v>
+      <c r="J43" t="s">
+        <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>66</v>
@@ -4793,13 +5075,15 @@
       <c r="A44" s="1">
         <v>100904</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>232</v>
+      <c r="B44" t="s">
+        <v>243</v>
       </c>
       <c r="C44" s="1">
         <v>1035</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="F44" s="1">
         <v>62</v>
       </c>
@@ -4812,11 +5096,11 @@
       <c r="I44" s="1">
         <v>4</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>88</v>
+      <c r="J44" t="s">
+        <v>90</v>
       </c>
       <c r="L44" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>66</v>
@@ -4835,13 +5119,15 @@
       <c r="A45" s="1">
         <v>100905</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>234</v>
+      <c r="B45" t="s">
+        <v>228</v>
       </c>
       <c r="C45" s="1">
         <v>1042</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="F45" s="1">
         <v>119</v>
       </c>
@@ -4854,11 +5140,11 @@
       <c r="I45" s="4">
         <v>3</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>88</v>
+      <c r="J45" t="s">
+        <v>90</v>
       </c>
       <c r="L45" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>66</v>
@@ -4877,14 +5163,14 @@
       <c r="A46" s="1">
         <v>100120</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>236</v>
+      <c r="B46" t="s">
+        <v>247</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>138</v>
+        <v>247</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="1">
@@ -4899,11 +5185,11 @@
       <c r="I46" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>237</v>
+      <c r="J46" t="s">
+        <v>90</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>66</v>
@@ -4920,12 +5206,12 @@
     </row>
     <row r="47" spans="1:17">
       <c r="L47" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="L48" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4948,37 +5234,37 @@
   <sheetData>
     <row r="4" s="1" customFormat="1" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>66</v>
@@ -4998,37 +5284,37 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>69</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>66</v>
@@ -5048,7 +5334,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:17">
@@ -5056,13 +5342,13 @@
         <v>100113</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>59</v>
@@ -5074,19 +5360,19 @@
         <v>134</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I20" s="1">
         <v>3</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>66</v>
